--- a/experimentos/lre/revision/hoja-quechua.xlsx
+++ b/experimentos/lre/revision/hoja-quechua.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -474,17 +474,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>QN001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>supi</t>
+          <t>yapa</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>pedo</t>
+          <t>adición, añadidura, aditamento</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -494,17 +494,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>QN002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>arwiy</t>
+          <t>machu</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>atar, ceñir</t>
+          <t>viejo, anciano</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -514,17 +514,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>QN003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>qasi</t>
+          <t>maki illapa</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>pistola, charpe</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -534,17 +534,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>QN004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>qurpachay</t>
+          <t>ninay</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>hospedar, alojar, albergar, acoger</t>
+          <t>quemar; encender fuego</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -554,17 +554,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>QN005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>millu</t>
+          <t>mayman</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>salado, salobre</t>
+          <t>adonde</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -574,17 +574,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>QN006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>allpayachiy</t>
+          <t>sama</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>moler, triturar</t>
+          <t>respiración, aliento, hálito</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -594,17 +594,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>QN007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>mask'ampuy</t>
+          <t>ismay</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ir a buscárselo</t>
+          <t>cagar, defecar</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -614,17 +614,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>QN008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>qispichiy</t>
+          <t>inqa</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>criar</t>
+          <t>rey</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -634,17 +634,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>QN009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>qapchapi qillqasqata watuy</t>
+          <t>ruwayman churay</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>descifrar</t>
+          <t>efectuar</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -654,17 +654,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>QN010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sumaq</t>
+          <t>ñawsa</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>hermoso, fermoso, bello</t>
+          <t>ciego, invidente</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -674,17 +674,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>QN011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>wayrachina</t>
+          <t>kallpanchay</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>alto horno</t>
+          <t>reforzar; fortalecer; vigorizar</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -694,17 +694,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>QN012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>chiqnipakuy</t>
+          <t>purun</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>aborrecer; detestar; abominar</t>
+          <t>salvaje, montaraz</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -714,17 +714,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>QN013</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>llakiy</t>
+          <t>urqu waka</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>sufrir, penar, padecer</t>
+          <t>toro</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -734,17 +734,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>QN014</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>lluqlla</t>
+          <t>challwa hap'iy</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>corrimiento de tierra, deslave</t>
+          <t>pescar</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -754,17 +754,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>QN015</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>chiqaqchay</t>
+          <t>ichik</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>elucidar</t>
+          <t>pequeño</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -774,17 +774,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>QN016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>yachakuq</t>
+          <t>chikichay</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>estudiante</t>
+          <t>distribuir</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -794,17 +794,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>QN017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>irpa</t>
+          <t>hap'ichiy</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>pichón</t>
+          <t>encender, encender fuego, prender fuego</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -814,17 +814,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>QN018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>chayanpuy</t>
+          <t>uquti</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>retornar, regresar, volver</t>
+          <t>ano, sisiflís</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -834,17 +834,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>QN019</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>para wayra</t>
+          <t>hawkay mit'a</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>procela</t>
+          <t>otoño</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
@@ -854,17 +854,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>QN020</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>aka</t>
+          <t>yachay wayllukuq</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>heces, feca</t>
+          <t>filósofo, filósofa</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -874,17 +874,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>QN021</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>rakiy</t>
+          <t>kay pacha</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>repartir</t>
+          <t>presente, actual, ahora</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -894,17 +894,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>QN022</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>khastuy</t>
+          <t>runayay</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>masticar; rumiar; pacer el ganado</t>
+          <t>llegar a ser hombre (o indígena)</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -914,17 +914,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>QN023</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>kasuruway</t>
+          <t>wasiyuq</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>obedecer</t>
+          <t>dueño de la casa</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
@@ -934,17 +934,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>QN024</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>pisqi muru</t>
+          <t>kuyuy</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>abalorio</t>
+          <t>mover; moverse; moverse; bambolarse</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
@@ -954,17 +954,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>QN025</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>kuskachay</t>
+          <t>malliy</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>acordar</t>
+          <t>probar</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -974,17 +974,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>QN026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>utaq</t>
+          <t>kañiy</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>también, asimismo, eso mismo</t>
+          <t>pagar</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
@@ -994,17 +994,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>QN027</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>qispichiy</t>
+          <t>isqun chunka</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>liberar, apelar</t>
+          <t>noventa</t>
         </is>
       </c>
       <c r="D28" s="2" t="n"/>
@@ -1014,17 +1014,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>QN028</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>hirq'i</t>
+          <t>siwulla</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>niño</t>
+          <t>cebolla</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1034,17 +1034,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>QN029</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>chakatarayay</t>
+          <t>qasikay</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ser crucificado</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="D30" s="2" t="n"/>
@@ -1054,17 +1054,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>QN030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>hutk'upuy</t>
+          <t>phukllay</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>agujereárselo</t>
+          <t>jugar; recrearse</t>
         </is>
       </c>
       <c r="D31" s="2" t="n"/>
@@ -1074,17 +1074,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>QN031</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ch'uñuchay</t>
+          <t>misk'i yaku</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>hacer chuño de tubérculos; deshidratar</t>
+          <t>jugo</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
@@ -1094,17 +1094,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>QN032</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>saqmanakuy</t>
+          <t>ñiyta munay</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>pugilismo</t>
+          <t>querer decir</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1114,17 +1114,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>QN033</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>mawk'achikuy</t>
+          <t>hampiy</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>dejar gastarse; gastarse sin sentirlo</t>
+          <t>curar</t>
         </is>
       </c>
       <c r="D34" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>QN034</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>qallway</t>
+          <t>laqha wasi</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>tupir los hilos en el tejido</t>
+          <t>cárcel, prisión, penitenciaría</t>
         </is>
       </c>
       <c r="D35" s="2" t="n"/>
@@ -1154,17 +1154,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>QN035</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>akshu</t>
+          <t>kaku</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>patata</t>
+          <t>tío</t>
         </is>
       </c>
       <c r="D36" s="2" t="n"/>
@@ -1174,17 +1174,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>QN036</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>qaqa</t>
+          <t>wislla</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>peña</t>
+          <t>cuchara, cucharón</t>
         </is>
       </c>
       <c r="D37" s="2" t="n"/>
@@ -1194,17 +1194,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>QN037</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>karunchakapuy</t>
+          <t>pallariy</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>abandonar; desamparar; dejar</t>
+          <t>recoger</t>
         </is>
       </c>
       <c r="D38" s="2" t="n"/>
@@ -1214,17 +1214,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>QN038</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>atillcha</t>
+          <t>paqta</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>amigo, amiga, chochera</t>
+          <t>igual, equiparable, equivalente</t>
         </is>
       </c>
       <c r="D39" s="2" t="n"/>
@@ -1234,17 +1234,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>QN039</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>q'ipina</t>
+          <t>kiki</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>saco, mochila</t>
+          <t>mismo, igual, equivalente</t>
         </is>
       </c>
       <c r="D40" s="2" t="n"/>
@@ -1254,17 +1254,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>QN040</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>yapa</t>
+          <t>iniy</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>una vez más, de nuevo, otra vez</t>
+          <t>creer; tener fe; dar credito</t>
         </is>
       </c>
       <c r="D41" s="2" t="n"/>
@@ -1274,17 +1274,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>QN041</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>kurikinka</t>
+          <t>phaway</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>caracara</t>
+          <t>volar, correr</t>
         </is>
       </c>
       <c r="D42" s="2" t="n"/>
@@ -1294,17 +1294,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>QN042</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>wuynas nuchis</t>
+          <t>qhipan pacha</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>buenas noches</t>
+          <t>futuro, porvenir</t>
         </is>
       </c>
       <c r="D43" s="2" t="n"/>
@@ -1314,17 +1314,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Q043</t>
+          <t>QN043</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>apu</t>
+          <t>hap'iqay</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>dios</t>
+          <t>entender</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -1334,17 +1334,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Q044</t>
+          <t>QN044</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ichhuna</t>
+          <t>hanay</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>hoz, falce, segur</t>
+          <t>cubrir con pañales</t>
         </is>
       </c>
       <c r="D45" s="2" t="n"/>
@@ -1354,17 +1354,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Q045</t>
+          <t>QN045</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ayqeykuy</t>
+          <t>wiyulin</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>parapetarse</t>
+          <t>violín</t>
         </is>
       </c>
       <c r="D46" s="2" t="n"/>
@@ -1374,17 +1374,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Q046</t>
+          <t>QN046</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>rumu</t>
+          <t>killmu</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>yuca</t>
+          <t>anaranjado, naranja, naranjoso</t>
         </is>
       </c>
       <c r="D47" s="2" t="n"/>
@@ -1394,17 +1394,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Q047</t>
+          <t>QN047</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>tarichiy</t>
+          <t>chullunku</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>hacer encontrar</t>
+          <t>hielo, del agua su duro</t>
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
@@ -1414,17 +1414,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Q048</t>
+          <t>QN048</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>marq'a</t>
+          <t>alli</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>brazo</t>
+          <t>bueno</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -1434,17 +1434,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Q049</t>
+          <t>QN049</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>irqita munay</t>
+          <t>thatkichiy</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>acariciar al niño</t>
+          <t>ayudar a dar pasos; hacer caminar al niño</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -1454,17 +1454,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>QN050</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>chichuyachiy</t>
+          <t>tupuy</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>hacer embarazar</t>
+          <t>medir, mensurar</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
@@ -1474,17 +1474,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Q051</t>
+          <t>QN051</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>pacha kuyuy</t>
+          <t>ñawra</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>seísmo</t>
+          <t>diversidad</t>
         </is>
       </c>
       <c r="D52" s="2" t="n"/>
@@ -1494,17 +1494,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Q052</t>
+          <t>QN052</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>q'uñi</t>
+          <t>paya</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>cálido, caluroso, calentito</t>
+          <t>vieja, anciana, viejita</t>
         </is>
       </c>
       <c r="D53" s="2" t="n"/>
@@ -1514,17 +1514,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Q053</t>
+          <t>QN053</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>k'ichkichiy</t>
+          <t>riqsiy</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>hacer estreñir</t>
+          <t>conocer, reconocer, examinar, identificar</t>
         </is>
       </c>
       <c r="D54" s="2" t="n"/>
@@ -1534,17 +1534,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Q054</t>
+          <t>QN054</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ruruy</t>
+          <t>khuchuy</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>dar fruta</t>
+          <t>cortar carne; cortar; cortar con cuchillo</t>
         </is>
       </c>
       <c r="D55" s="2" t="n"/>
@@ -1554,17 +1554,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Q055</t>
+          <t>QN055</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>kuyuy</t>
+          <t>kinsa k'uchu</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>mover; moverse; moverse; bambolarse</t>
+          <t>triángulo</t>
         </is>
       </c>
       <c r="D56" s="2" t="n"/>
@@ -1574,17 +1574,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Q056</t>
+          <t>QN056</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>llaqwa</t>
+          <t>killa</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>llajua</t>
+          <t>luna</t>
         </is>
       </c>
       <c r="D57" s="2" t="n"/>
@@ -1594,17 +1594,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Q057</t>
+          <t>QN057</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>gogo</t>
+          <t>qunqay</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>sapo, sapa</t>
+          <t>olvidar, perder el recuerdo</t>
         </is>
       </c>
       <c r="D58" s="2" t="n"/>
@@ -1614,17 +1614,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Q058</t>
+          <t>QN058</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>kamay</t>
+          <t>chunka kimsayuq</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>crear, generar</t>
+          <t>trece</t>
         </is>
       </c>
       <c r="D59" s="2" t="n"/>
@@ -1634,17 +1634,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Q059</t>
+          <t>QN059</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>hatarichikuy</t>
+          <t>napaykuy</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>construirse o edificarse algo</t>
+          <t>saludar; felicitar</t>
         </is>
       </c>
       <c r="D60" s="2" t="n"/>
@@ -1654,17 +1654,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Q060</t>
+          <t>QN060</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>qhachway</t>
+          <t>sisa</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>bailar</t>
+          <t>flor</t>
         </is>
       </c>
       <c r="D61" s="2" t="n"/>
@@ -1674,17 +1674,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Q061</t>
+          <t>QN061</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>kuyuy</t>
+          <t>ninri</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>torcer la soguilla</t>
+          <t>{{t+|es|oreja|f}, oído</t>
         </is>
       </c>
       <c r="D62" s="2" t="n"/>
@@ -1694,17 +1694,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Q062</t>
+          <t>QN062</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>watuy</t>
+          <t>wanay</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>profecía</t>
+          <t>escarmentar; corregir</t>
         </is>
       </c>
       <c r="D63" s="2" t="n"/>
@@ -1714,17 +1714,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Q063</t>
+          <t>QN063</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>yanayay</t>
+          <t>utqay</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>oscurecimiento</t>
+          <t>apresurarse, apurarse, darse prisa</t>
         </is>
       </c>
       <c r="D64" s="2" t="n"/>
@@ -1734,17 +1734,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Q064</t>
+          <t>QN064</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>llulluy</t>
+          <t>hanan</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>alustrar</t>
+          <t>alto, elevado, en lo alto</t>
         </is>
       </c>
       <c r="D65" s="2" t="n"/>
@@ -1754,17 +1754,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Q065</t>
+          <t>QN065</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>churakuy</t>
+          <t>tupachiy</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ponerse; usar (ropa); ponerse la ropa</t>
+          <t>hacer topar con algo, encontrar</t>
         </is>
       </c>
       <c r="D66" s="2" t="n"/>
@@ -1774,17 +1774,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Q066</t>
+          <t>QN066</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>llamp'uchay</t>
+          <t>yatana qallwa</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>ablandar; volver apacible</t>
+          <t>piano</t>
         </is>
       </c>
       <c r="D67" s="2" t="n"/>
@@ -1794,17 +1794,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Q067</t>
+          <t>QN067</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>muchuy</t>
+          <t>kuraq</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>sufrir</t>
+          <t>anciano, adulto mayor</t>
         </is>
       </c>
       <c r="D68" s="2" t="n"/>
@@ -1814,17 +1814,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Q068</t>
+          <t>QN068</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>nuna</t>
+          <t>pirqay</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>espíritu, alma, pneuma</t>
+          <t>construir muros</t>
         </is>
       </c>
       <c r="D69" s="2" t="n"/>
@@ -1834,17 +1834,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Q069</t>
+          <t>QN069</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>tarikuy</t>
+          <t>hurquy</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>encontrarlos; encontrar algo</t>
+          <t>quitar, remover, toller</t>
         </is>
       </c>
       <c r="D70" s="2" t="n"/>
@@ -1854,17 +1854,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Q070</t>
+          <t>QN070</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>tupachiy</t>
+          <t>qhuya</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>hacer topar con algo, encontrar</t>
+          <t>mina</t>
         </is>
       </c>
       <c r="D71" s="2" t="n"/>
@@ -1874,17 +1874,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Q071</t>
+          <t>QN071</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>chiqniy</t>
+          <t>paway</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>odiar; aborrecer; despreciar</t>
+          <t>organizar</t>
         </is>
       </c>
       <c r="D72" s="2" t="n"/>
@@ -1894,17 +1894,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Q072</t>
+          <t>QN072</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>qillqapuy</t>
+          <t>suñay</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>escribírselo</t>
+          <t>regalar; obsequiar</t>
         </is>
       </c>
       <c r="D73" s="2" t="n"/>
@@ -1914,17 +1914,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Q073</t>
+          <t>QN073</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>chullunku</t>
+          <t>tawa chunka hukniyuq</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>hielo, del agua su duro</t>
+          <t>cuarenta y uno</t>
         </is>
       </c>
       <c r="D74" s="2" t="n"/>
@@ -1934,17 +1934,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q074</t>
+          <t>QN074</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>wiksallikuy</t>
+          <t>karka</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>concebir</t>
+          <t>esqueleto, osamenta, osatura</t>
         </is>
       </c>
       <c r="D75" s="2" t="n"/>
@@ -1954,17 +1954,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Q075</t>
+          <t>QN075</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>wayrachikuy</t>
+          <t>kutichiy</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>abanicarse</t>
+          <t>vomitar, restituir, vomitar</t>
         </is>
       </c>
       <c r="D76" s="2" t="n"/>
@@ -1974,17 +1974,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Q076</t>
+          <t>QN076</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>kai</t>
+          <t>wisku</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>estar, radicar</t>
+          <t>abarca</t>
         </is>
       </c>
       <c r="D77" s="2" t="n"/>
@@ -1994,17 +1994,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Q077</t>
+          <t>QN077</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>kuru</t>
+          <t>taki</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>oruga, cuncuna, convólvulo</t>
+          <t>canción, rola</t>
         </is>
       </c>
       <c r="D78" s="2" t="n"/>
@@ -2014,17 +2014,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Q078</t>
+          <t>QN078</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ayway</t>
+          <t>ancha</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>moverse</t>
+          <t>muy, mucho, más</t>
         </is>
       </c>
       <c r="D79" s="2" t="n"/>
@@ -2034,17 +2034,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Q079</t>
+          <t>QN079</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>akllakuy</t>
+          <t>maymanta</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>elegir</t>
+          <t>de/desde donde, onde</t>
         </is>
       </c>
       <c r="D80" s="2" t="n"/>
@@ -2054,17 +2054,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Q080</t>
+          <t>QN080</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ichhu</t>
+          <t>ranqhay</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>paja</t>
+          <t>vender; regatear; expender</t>
         </is>
       </c>
       <c r="D81" s="2" t="n"/>
@@ -2074,17 +2074,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Q081</t>
+          <t>QN081</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>uku</t>
+          <t>nuna</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>hondo</t>
+          <t>alma, pneuma</t>
         </is>
       </c>
       <c r="D82" s="2" t="n"/>
@@ -2094,17 +2094,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Q082</t>
+          <t>QN082</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>qasa</t>
+          <t>chhalla</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>escarcha, helada, carama</t>
+          <t>ligero, liviano</t>
         </is>
       </c>
       <c r="D83" s="2" t="n"/>
@@ -2114,17 +2114,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Q083</t>
+          <t>QN083</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>muchuy</t>
+          <t>lampay</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>pobreza, pauperismo, mishiadura</t>
+          <t>trabajar con pala; palear</t>
         </is>
       </c>
       <c r="D84" s="2" t="n"/>
@@ -2134,17 +2134,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Q084</t>
+          <t>QN084</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>qulluchiy</t>
+          <t>yuyaychay</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>hacer inundar</t>
+          <t>aconsejar, guiar, orientar, asesorar</t>
         </is>
       </c>
       <c r="D85" s="2" t="n"/>
@@ -2154,17 +2154,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Q085</t>
+          <t>QN085</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>ñawpa kayninman kutichiy</t>
+          <t>ch'antay</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>reducir</t>
+          <t>unir, uñir, aunar</t>
         </is>
       </c>
       <c r="D86" s="2" t="n"/>
@@ -2174,17 +2174,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Q086</t>
+          <t>QN086</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>rikuriy</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>blando, muelle, mole</t>
+          <t>parecer</t>
         </is>
       </c>
       <c r="D87" s="2" t="n"/>
@@ -2194,17 +2194,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Q087</t>
+          <t>QN087</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>yanapay</t>
+          <t>umalliy</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ayudar</t>
+          <t>razonar; imaginar</t>
         </is>
       </c>
       <c r="D88" s="2" t="n"/>
@@ -2214,17 +2214,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Q088</t>
+          <t>QN088</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>waqatiyay</t>
+          <t>hatun qucha</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>acobardarse</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="D89" s="2" t="n"/>
@@ -2234,17 +2234,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Q089</t>
+          <t>QN089</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>iskay chunka hukniyuq</t>
+          <t>tullu</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>veintiuno</t>
+          <t>flaco</t>
         </is>
       </c>
       <c r="D90" s="2" t="n"/>
@@ -2254,17 +2254,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Q090</t>
+          <t>QN090</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>puririchiy</t>
+          <t>chilltu</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>para transportar</t>
+          <t>tomate, jitomate</t>
         </is>
       </c>
       <c r="D91" s="2" t="n"/>
@@ -2274,17 +2274,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Q091</t>
+          <t>QN091</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>maymanta</t>
+          <t>tanta</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>de/desde donde, onde</t>
+          <t>junto, yunto</t>
         </is>
       </c>
       <c r="D92" s="2" t="n"/>
@@ -2294,17 +2294,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Q092</t>
+          <t>QN092</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>p'itapuy</t>
+          <t>tiyu</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>tejérselo (labores de punto)</t>
+          <t>arena</t>
         </is>
       </c>
       <c r="D93" s="2" t="n"/>
@@ -2314,17 +2314,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Q093</t>
+          <t>QN093</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>mirachiy</t>
+          <t>ariq</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>multiplicar</t>
+          <t>volcán</t>
         </is>
       </c>
       <c r="D94" s="2" t="n"/>
@@ -2334,17 +2334,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Q094</t>
+          <t>QN094</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>nuna</t>
+          <t>mana allin</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>alma, pneuma</t>
+          <t>malo</t>
         </is>
       </c>
       <c r="D95" s="2" t="n"/>
@@ -2354,17 +2354,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Q095</t>
+          <t>QN095</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ch'ipihyay</t>
+          <t>pichay</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>guiñar, cucar, bizquear</t>
+          <t>limpiar</t>
         </is>
       </c>
       <c r="D96" s="2" t="n"/>
@@ -2374,17 +2374,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Q096</t>
+          <t>QN096</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>yachay</t>
+          <t>awqanakuy</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>saber</t>
+          <t>guerrear, hacer la guerra</t>
         </is>
       </c>
       <c r="D97" s="2" t="n"/>
@@ -2394,17 +2394,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Q097</t>
+          <t>QN097</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>qulluchiy</t>
+          <t>ruway</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>exterminar, frustrar, destruir</t>
+          <t>hacer</t>
         </is>
       </c>
       <c r="D98" s="2" t="n"/>
@@ -2414,17 +2414,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Q098</t>
+          <t>QN098</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>alqamari</t>
+          <t>paray</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>caracará, carancho</t>
+          <t>llover</t>
         </is>
       </c>
       <c r="D99" s="2" t="n"/>
@@ -2434,17 +2434,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Q099</t>
+          <t>QN099</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>pisipay</t>
+          <t>apay</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>cansar, cansarse</t>
+          <t>llevar, cargar, acarrear</t>
         </is>
       </c>
       <c r="D100" s="2" t="n"/>
@@ -2454,17 +2454,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Q100</t>
+          <t>QN100</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>qichuy</t>
+          <t>llamp'u</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>sustraer; quitar</t>
+          <t>pacífico, manso, dócil</t>
         </is>
       </c>
       <c r="D101" s="2" t="n"/>
@@ -2474,17 +2474,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Q101</t>
+          <t>QN101</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>ch'umpi</t>
+          <t>umalli</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>pardo</t>
+          <t>artículo</t>
         </is>
       </c>
       <c r="D102" s="2" t="n"/>
@@ -2494,17 +2494,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Q102</t>
+          <t>QN102</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>palta</t>
+          <t>lawa</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>aguacate</t>
+          <t>sopa, caldo</t>
         </is>
       </c>
       <c r="D103" s="2" t="n"/>
@@ -2514,17 +2514,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Q103</t>
+          <t>QN103</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>aiwai</t>
+          <t>ayñiy</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>irse, marcharse, alejarse</t>
+          <t>contradecir, oponerse, rezongar</t>
         </is>
       </c>
       <c r="D104" s="2" t="n"/>
@@ -2534,17 +2534,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Q104</t>
+          <t>QN104</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>tipiy</t>
+          <t>riti</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>cosechar</t>
+          <t>nieve</t>
         </is>
       </c>
       <c r="D105" s="2" t="n"/>
@@ -2554,17 +2554,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Q105</t>
+          <t>QN105</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>tupu</t>
+          <t>pachak</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>medida</t>
+          <t>centuria, siglo</t>
         </is>
       </c>
       <c r="D106" s="2" t="n"/>
@@ -2574,17 +2574,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Q106</t>
+          <t>QN106</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>piñi</t>
+          <t>llapan</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>abalorio</t>
+          <t>todos, todo el mundo, todo quisqui</t>
         </is>
       </c>
       <c r="D107" s="2" t="n"/>
@@ -2594,17 +2594,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Q107</t>
+          <t>QN107</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>rantikuy</t>
+          <t>waka</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>vender; negociar, ofrecer</t>
+          <t>vaca</t>
         </is>
       </c>
       <c r="D108" s="2" t="n"/>
@@ -2614,17 +2614,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Q108</t>
+          <t>QN108</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>qatiy</t>
+          <t>yaya</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>arrear ganado</t>
+          <t>tío</t>
         </is>
       </c>
       <c r="D109" s="2" t="n"/>
@@ -2634,17 +2634,17 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Q109</t>
+          <t>QN109</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>suwakuy</t>
+          <t>hanu k'ara</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>robar</t>
+          <t>lepidium, hierba de la pimienta</t>
         </is>
       </c>
       <c r="D110" s="2" t="n"/>
@@ -2654,17 +2654,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Q110</t>
+          <t>QN110</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>churana</t>
+          <t>q'ispi</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>armario</t>
+          <t>claro</t>
         </is>
       </c>
       <c r="D111" s="2" t="n"/>
@@ -2674,17 +2674,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Q111</t>
+          <t>QN111</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>aslla</t>
+          <t>hanaq</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>pequeño</t>
+          <t>alto, elevado, en lo alto</t>
         </is>
       </c>
       <c r="D112" s="2" t="n"/>
@@ -2694,17 +2694,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Q112</t>
+          <t>QN112</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>wata</t>
+          <t>hiwiy</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>año</t>
+          <t>reducir</t>
         </is>
       </c>
       <c r="D113" s="2" t="n"/>
@@ -2714,17 +2714,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Q113</t>
+          <t>QN113</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>quchikuy</t>
+          <t>upa</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ordenar</t>
+          <t>mudo</t>
         </is>
       </c>
       <c r="D114" s="2" t="n"/>
@@ -2734,17 +2734,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Q114</t>
+          <t>QN114</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>kañay</t>
+          <t>allin tuta</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>recalentar; requemar</t>
+          <t>buenas noches</t>
         </is>
       </c>
       <c r="D115" s="2" t="n"/>
@@ -2754,17 +2754,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Q115</t>
+          <t>QN115</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>irpa</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>paloma, pichón</t>
+          <t>temer, tener miedo, espantarse, asustarse</t>
         </is>
       </c>
       <c r="D116" s="2" t="n"/>
@@ -2774,17 +2774,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Q116</t>
+          <t>QN116</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>pawai</t>
+          <t>qaramuy</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>volar, circunvolar</t>
+          <t>ir a dar de comer; ir a servir comida</t>
         </is>
       </c>
       <c r="D117" s="2" t="n"/>
@@ -2794,17 +2794,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Q117</t>
+          <t>QN117</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>mañay</t>
+          <t>yupa</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>exigir, demandar, intimar</t>
+          <t>abundante, copioso, cuantioso</t>
         </is>
       </c>
       <c r="D118" s="2" t="n"/>
@@ -2814,17 +2814,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Q118</t>
+          <t>QN118</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>illapa</t>
+          <t>chapaq</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>relámpago, rayo, fucilazo</t>
+          <t>policía, tombería</t>
         </is>
       </c>
       <c r="D119" s="2" t="n"/>
@@ -2834,17 +2834,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Q119</t>
+          <t>QN119</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>wañurqachiy</t>
+          <t>qurpachay</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>asesinar; matar</t>
+          <t>hospedar, alojar, albergar, acoger</t>
         </is>
       </c>
       <c r="D120" s="2" t="n"/>
@@ -2854,17 +2854,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Q120</t>
+          <t>QN120</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>puytu</t>
+          <t>kunan</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>rombo</t>
+          <t>ahora</t>
         </is>
       </c>
       <c r="D121" s="2" t="n"/>
@@ -2874,17 +2874,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Q121</t>
+          <t>QN121</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>qaqapay</t>
+          <t>suqta chunka</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>despeñar</t>
+          <t>sesenta</t>
         </is>
       </c>
       <c r="D122" s="2" t="n"/>
@@ -2894,17 +2894,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Q122</t>
+          <t>QN122</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>kuskiy</t>
+          <t>lluqsichiy</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>barbechar</t>
+          <t>sacar, echar, arrojar, obligar a salir</t>
         </is>
       </c>
       <c r="D123" s="2" t="n"/>
@@ -2914,17 +2914,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Q123</t>
+          <t>QN123</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>manka</t>
+          <t>qaqa</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>olla</t>
+          <t>peña</t>
         </is>
       </c>
       <c r="D124" s="2" t="n"/>
@@ -2934,17 +2934,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Q124</t>
+          <t>QN124</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>achanqaray</t>
+          <t>ruray</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>(Begonia) Begonia</t>
+          <t>formar</t>
         </is>
       </c>
       <c r="D125" s="2" t="n"/>
@@ -2954,17 +2954,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Q125</t>
+          <t>QN125</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>chakuy</t>
+          <t>hunu</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>cazar</t>
+          <t>millón</t>
         </is>
       </c>
       <c r="D126" s="2" t="n"/>
@@ -2974,17 +2974,17 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Q126</t>
+          <t>QN126</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>paqpa</t>
+          <t>achkachay</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>fibra, brenca</t>
+          <t>aumentar; acrecentar</t>
         </is>
       </c>
       <c r="D127" s="2" t="n"/>
@@ -2994,17 +2994,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Q127</t>
+          <t>QN127</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>wila</t>
+          <t>takiy</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>vela, candela, cirio</t>
+          <t>canción, rola</t>
         </is>
       </c>
       <c r="D128" s="2" t="n"/>
@@ -3014,17 +3014,17 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Q128</t>
+          <t>QN128</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>kuskachay</t>
+          <t>churakuy</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>balancear; guardar el equilibrio</t>
+          <t>ponerse; usar (ropa); ponerse la ropa</t>
         </is>
       </c>
       <c r="D129" s="2" t="n"/>
@@ -3034,17 +3034,17 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Q129</t>
+          <t>QN129</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>tapuchiy</t>
+          <t>llamkana</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>hacer preguntar con alguien</t>
+          <t>herramienta</t>
         </is>
       </c>
       <c r="D130" s="2" t="n"/>
@@ -3054,17 +3054,17 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Q130</t>
+          <t>QN130</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>maki</t>
+          <t>yachachisqa</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>mano</t>
+          <t>alumno, estudiante, discente</t>
         </is>
       </c>
       <c r="D131" s="2" t="n"/>
@@ -3074,17 +3074,17 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Q131</t>
+          <t>QN131</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>wañuy</t>
+          <t>iñiy</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>perecer</t>
+          <t>creer; tener fe; dar credito</t>
         </is>
       </c>
       <c r="D132" s="2" t="n"/>
@@ -3094,17 +3094,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Q132</t>
+          <t>QN132</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>pallway</t>
+          <t>kasukuy</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>concluir, acabar, terminar un trabajo</t>
+          <t>obedecer</t>
         </is>
       </c>
       <c r="D133" s="2" t="n"/>
@@ -3114,17 +3114,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Q133</t>
+          <t>QN133</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>nikuy</t>
+          <t>thanta</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>pedir</t>
+          <t>usado, gastado</t>
         </is>
       </c>
       <c r="D134" s="2" t="n"/>
@@ -3134,17 +3134,17 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Q134</t>
+          <t>QN134</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>ninay</t>
+          <t>yuyayta hap'iy</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>quemar; encender fuego</t>
+          <t>entender</t>
         </is>
       </c>
       <c r="D135" s="2" t="n"/>
@@ -3154,17 +3154,17 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Q135</t>
+          <t>QN135</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>watukuy</t>
+          <t>pacha kuti</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>visitar</t>
+          <t>Regreso del tiempo, cambio social</t>
         </is>
       </c>
       <c r="D136" s="2" t="n"/>
@@ -3174,17 +3174,17 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Q136</t>
+          <t>QN136</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>arawiy</t>
+          <t>yuyay quy</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>hacer canciones; componer versos</t>
+          <t>aconsejar, guiar, orientar, asesorar</t>
         </is>
       </c>
       <c r="D137" s="2" t="n"/>
@@ -3194,17 +3194,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Q137</t>
+          <t>QN137</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>mayllakuy</t>
+          <t>yachakuq</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>lavarse</t>
+          <t>alumno, alumna, pupilo</t>
         </is>
       </c>
       <c r="D138" s="2" t="n"/>
@@ -3214,17 +3214,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Q138</t>
+          <t>QN138</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>watay</t>
+          <t>pukllay</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>adjuntar, atachar, atachear</t>
+          <t>jugar; recrearse</t>
         </is>
       </c>
       <c r="D139" s="2" t="n"/>
@@ -3234,17 +3234,17 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Q139</t>
+          <t>QN139</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>anta</t>
+          <t>hak'akllu</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>cobre</t>
+          <t>pájaro carpintero, pito, picamaderos</t>
         </is>
       </c>
       <c r="D140" s="2" t="n"/>
@@ -3254,17 +3254,17 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Q140</t>
+          <t>QN140</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>hallpa</t>
+          <t>ch'uspa</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>patria, terruño</t>
+          <t>bolsa</t>
         </is>
       </c>
       <c r="D141" s="2" t="n"/>
@@ -3274,17 +3274,17 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Q141</t>
+          <t>QN141</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>kiki</t>
+          <t>p'anqa</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>mismo, igual, equivalente</t>
+          <t>libro</t>
         </is>
       </c>
       <c r="D142" s="2" t="n"/>
@@ -3294,17 +3294,17 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Q142</t>
+          <t>QN142</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>watuy</t>
+          <t>machay</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>hechizar</t>
+          <t>beber, tomar, trincar</t>
         </is>
       </c>
       <c r="D143" s="2" t="n"/>
@@ -3314,17 +3314,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Q143</t>
+          <t>QN143</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>llamkana</t>
+          <t>umapi hap'iy</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>herramienta</t>
+          <t>entender; comprender; memorizar</t>
         </is>
       </c>
       <c r="D144" s="2" t="n"/>
@@ -3334,17 +3334,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Q144</t>
+          <t>QN144</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>pataray</t>
+          <t>qhulla puquy killa</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>doblar; plegar; doblar ropas</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="D145" s="2" t="n"/>
@@ -3354,17 +3354,17 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Q145</t>
+          <t>QN145</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>chukiy</t>
+          <t>yanay</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>tupir los hilos en el tejido</t>
+          <t>acompañar, comprobar, servir</t>
         </is>
       </c>
       <c r="D146" s="2" t="n"/>
@@ -3374,17 +3374,17 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Q146</t>
+          <t>QN146</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ñuñuchiy</t>
+          <t>kawsay</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>amamantar, dar la madre el pecho al hijo</t>
+          <t>vida</t>
         </is>
       </c>
       <c r="D147" s="2" t="n"/>
@@ -3394,17 +3394,17 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Q147</t>
+          <t>QN147</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>yapay</t>
+          <t>unu</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>aditar, añadir, allegar</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="D148" s="2" t="n"/>
@@ -3414,17 +3414,17 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Q148</t>
+          <t>QN148</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>t'inkuy</t>
+          <t>pachak waranqa</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>venir justo (ropa)</t>
+          <t>cien mil</t>
         </is>
       </c>
       <c r="D149" s="2" t="n"/>
@@ -3434,17 +3434,17 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Q149</t>
+          <t>QN149</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>lanq'i</t>
+          <t>yachachiy</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>huarache, sandália</t>
+          <t>adiestrar, enseñar a, instruir</t>
         </is>
       </c>
       <c r="D150" s="2" t="n"/>
@@ -3454,17 +3454,17 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Q150</t>
+          <t>QN150</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>waqyapuy</t>
+          <t>sapra</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>llamárselo</t>
+          <t>barba</t>
         </is>
       </c>
       <c r="D151" s="2" t="n"/>
@@ -3474,17 +3474,17 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Q151</t>
+          <t>QN151</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>yapa</t>
+          <t>waqyay</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>adición, añadidura, aditamento</t>
+          <t>llamar, citar, anunciar</t>
         </is>
       </c>
       <c r="D152" s="2" t="n"/>
@@ -3494,17 +3494,17 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Q152</t>
+          <t>QN152</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>sinqa</t>
+          <t>tawna</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>nariz</t>
+          <t>bastón</t>
         </is>
       </c>
       <c r="D153" s="2" t="n"/>
@@ -3514,17 +3514,17 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Q153</t>
+          <t>QN153</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ch'iqmichiy</t>
+          <t>wichay</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>disgustar, afligir, atormentar</t>
+          <t>ascender</t>
         </is>
       </c>
       <c r="D154" s="2" t="n"/>
@@ -3534,17 +3534,17 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Q154</t>
+          <t>QN154</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>apuski</t>
+          <t>t'uqyay</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>antepasado, ancestro</t>
+          <t>pronunciar</t>
         </is>
       </c>
       <c r="D155" s="2" t="n"/>
@@ -3554,17 +3554,17 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Q155</t>
+          <t>QN155</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>llik'iy</t>
+          <t>wanu</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>romper, quebrar, escrachar</t>
+          <t>abono</t>
         </is>
       </c>
       <c r="D156" s="2" t="n"/>
@@ -3574,7 +3574,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Q156</t>
+          <t>QN156</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -3594,17 +3594,17 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Q157</t>
+          <t>QN157</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>qhanqayachiy</t>
+          <t>kamayuq</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>hacer volver grande o estirar</t>
+          <t>especialista</t>
         </is>
       </c>
       <c r="D158" s="2" t="n"/>
@@ -3614,17 +3614,17 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Q158</t>
+          <t>QN158</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>p'atanchay</t>
+          <t>wasichay</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>uniformar</t>
+          <t>hacer casa, edificar, construir una casa</t>
         </is>
       </c>
       <c r="D159" s="2" t="n"/>
@@ -3634,17 +3634,17 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Q159</t>
+          <t>QN159</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>kunka</t>
+          <t>michiy runata</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>cuello</t>
+          <t>gobernar</t>
         </is>
       </c>
       <c r="D160" s="2" t="n"/>
@@ -3654,17 +3654,17 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Q160</t>
+          <t>QN160</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>sulluy</t>
+          <t>llaqta kamay</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>aborto, aborto espontáneo, aborto natural</t>
+          <t>alcaldía</t>
         </is>
       </c>
       <c r="D161" s="2" t="n"/>
@@ -3674,17 +3674,17 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Q161</t>
+          <t>QN161</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>llulla</t>
+          <t>ñawi</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>mentira, embuste, cáshpira</t>
+          <t>ojo</t>
         </is>
       </c>
       <c r="D162" s="2" t="n"/>
@@ -3694,17 +3694,17 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Q162</t>
+          <t>QN162</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>kutichiy</t>
+          <t>rakiy</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>retornar</t>
+          <t>dividir; fraccionar</t>
         </is>
       </c>
       <c r="D163" s="2" t="n"/>
@@ -3714,17 +3714,17 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Q163</t>
+          <t>QN163</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>suñay</t>
+          <t>allquchay</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>regalar; obsequiar</t>
+          <t>abusar; violar (sexual); maltratar; abusar</t>
         </is>
       </c>
       <c r="D164" s="2" t="n"/>
@@ -3734,17 +3734,17 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Q164</t>
+          <t>QN164</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>hatun tayta</t>
+          <t>supi</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>abuelo</t>
+          <t>pedo</t>
         </is>
       </c>
       <c r="D165" s="2" t="n"/>
@@ -3754,17 +3754,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Q165</t>
+          <t>QN165</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>pillachay</t>
+          <t>ñawinchay</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>desigualar</t>
+          <t>leer</t>
         </is>
       </c>
       <c r="D166" s="2" t="n"/>
@@ -3774,17 +3774,17 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Q166</t>
+          <t>QN166</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>suwaq'ara</t>
+          <t>karru</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>zopilote</t>
+          <t>automóvil, auto, carro</t>
         </is>
       </c>
       <c r="D167" s="2" t="n"/>
@@ -3794,17 +3794,17 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Q167</t>
+          <t>QN167</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>yaykuchiy</t>
+          <t>tawa k'uchu</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>hacer entrar, introducir, introducir</t>
+          <t>cuadrado</t>
         </is>
       </c>
       <c r="D168" s="2" t="n"/>
@@ -3814,17 +3814,17 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Q168</t>
+          <t>QN168</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>phalluy</t>
+          <t>uma</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>destruir por medio de golpes físicos</t>
+          <t>cabeza</t>
         </is>
       </c>
       <c r="D169" s="2" t="n"/>
@@ -3834,17 +3834,17 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Q169</t>
+          <t>QN169</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ayqiy</t>
+          <t>yañay</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>huir, evadir, fugar</t>
+          <t>experimentar</t>
         </is>
       </c>
       <c r="D170" s="2" t="n"/>
@@ -3854,17 +3854,17 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Q170</t>
+          <t>QN170</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>urqu waka</t>
+          <t>pitay</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>toro</t>
+          <t>fumar</t>
         </is>
       </c>
       <c r="D171" s="2" t="n"/>
@@ -3874,17 +3874,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Q171</t>
+          <t>QN171</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>illay</t>
+          <t>suntur</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>brillar, lucir</t>
+          <t>consejo</t>
         </is>
       </c>
       <c r="D172" s="2" t="n"/>
@@ -3894,17 +3894,17 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Q172</t>
+          <t>QN172</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>isku</t>
+          <t>amañay</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>cal</t>
+          <t>practicar; ejercitar; adaptar</t>
         </is>
       </c>
       <c r="D173" s="2" t="n"/>
@@ -3914,17 +3914,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Q173</t>
+          <t>QN173</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>hukhinachiy</t>
+          <t>wawqi</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>desfigurar</t>
+          <t>hermano</t>
         </is>
       </c>
       <c r="D174" s="2" t="n"/>
@@ -3934,17 +3934,17 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Q174</t>
+          <t>QN174</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>kapas</t>
+          <t>q'uñi</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>quizá</t>
+          <t>cálido, caluroso, calentito</t>
         </is>
       </c>
       <c r="D175" s="2" t="n"/>
@@ -3954,17 +3954,17 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Q175</t>
+          <t>QN175</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>unquna wasi</t>
+          <t>hayay</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>hospital, nosocomio</t>
+          <t>quemar (comida picante), picar, amargar</t>
         </is>
       </c>
       <c r="D176" s="2" t="n"/>
@@ -3974,17 +3974,17 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Q176</t>
+          <t>QN176</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>ñawpaq</t>
+          <t>aslla</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>último, pasado, anterior</t>
+          <t>pequeño</t>
         </is>
       </c>
       <c r="D177" s="2" t="n"/>
@@ -3994,17 +3994,17 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Q177</t>
+          <t>QN177</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>allqu</t>
+          <t>rimachiy</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>perro</t>
+          <t>conversar, dejar hablar, hacer confesar</t>
         </is>
       </c>
       <c r="D178" s="2" t="n"/>
@@ -4014,17 +4014,17 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Q178</t>
+          <t>QN178</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>iskay chunka isqunniyuq</t>
+          <t>manaraq</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>veintinueve</t>
+          <t>todavía no, aún no</t>
         </is>
       </c>
       <c r="D179" s="2" t="n"/>
@@ -4034,17 +4034,17 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Q179</t>
+          <t>QN179</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>hirai</t>
+          <t>llasay</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>coser</t>
+          <t>pesar</t>
         </is>
       </c>
       <c r="D180" s="2" t="n"/>
@@ -4054,17 +4054,17 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Q180</t>
+          <t>QN180</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>yachapayay</t>
+          <t>uku</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>remedar; imitar; parodiar</t>
+          <t>hondo</t>
         </is>
       </c>
       <c r="D181" s="2" t="n"/>
@@ -4074,17 +4074,17 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Q181</t>
+          <t>QN181</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>ismuy</t>
+          <t>siqay</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>pudrirse, podrirse</t>
+          <t>escalar, subir</t>
         </is>
       </c>
       <c r="D182" s="2" t="n"/>
@@ -4094,17 +4094,17 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Q182</t>
+          <t>QN182</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>q'ulluriy</t>
+          <t>ñawpa kayninman kutichiy</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>arremangar</t>
+          <t>reducir</t>
         </is>
       </c>
       <c r="D183" s="2" t="n"/>
@@ -4114,369 +4114,29 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Q183</t>
+          <t>QN183</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>yachay</t>
+          <t>phuti</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>aprender, escarmentar</t>
+          <t>pesar, pesadumbre, pena</t>
         </is>
       </c>
       <c r="D184" s="2" t="n"/>
       <c r="E184" s="2" t="n"/>
       <c r="F184" s="2" t="n"/>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>Q184</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>turikuy</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>resistir fisicamente</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" s="2" t="n"/>
-      <c r="F185" s="2" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>Q185</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>chaka tullu</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>fémur</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" s="2" t="n"/>
-      <c r="F186" s="2" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>Q186</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>tanta</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>junto, yunto</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="n"/>
-      <c r="E187" s="2" t="n"/>
-      <c r="F187" s="2" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>Q187</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>allin sonqo</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>benevolencia</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="n"/>
-      <c r="E188" s="2" t="n"/>
-      <c r="F188" s="2" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>Q188</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>hawipuy</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>untárselo</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" s="2" t="n"/>
-      <c r="F189" s="2" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>Q189</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>ispinku</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>trébol</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" s="2" t="n"/>
-      <c r="F190" s="2" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>Q190</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>ñan</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>carretera, calzada</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" s="2" t="n"/>
-      <c r="F191" s="2" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Q191</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>phaway</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>huir</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="n"/>
-      <c r="E192" s="2" t="n"/>
-      <c r="F192" s="2" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>Q192</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>k'uskiy</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>examinar, investigar, analizar, escudriñar</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" s="2" t="n"/>
-      <c r="F193" s="2" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Q193</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>arwiy</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>confundir</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="n"/>
-      <c r="E194" s="2" t="n"/>
-      <c r="F194" s="2" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>Q194</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>chipchiy</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>alustrar</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="n"/>
-      <c r="E195" s="2" t="n"/>
-      <c r="F195" s="2" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>Q195</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>mayway</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>enamorar</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="n"/>
-      <c r="E196" s="2" t="n"/>
-      <c r="F196" s="2" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>Q196</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>llasay</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>pesar</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="n"/>
-      <c r="E197" s="2" t="n"/>
-      <c r="F197" s="2" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Q197</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>tiyu</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>arena</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="n"/>
-      <c r="E198" s="2" t="n"/>
-      <c r="F198" s="2" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>Q198</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>suyakuy</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>esperar; tener esperanza</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="n"/>
-      <c r="E199" s="2" t="n"/>
-      <c r="F199" s="2" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Q199</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>kiki</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>uno mismo</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="n"/>
-      <c r="E200" s="2" t="n"/>
-      <c r="F200" s="2" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>Q200</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>nanaq</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>robusto</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="n"/>
-      <c r="E201" s="2" t="n"/>
-      <c r="F201" s="2" t="n"/>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="D2:D201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elija sí, parcial o no." type="list">
+    <dataValidation sqref="D2:D184" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elija sí, parcial o no." type="list">
       <formula1>"sí,parcial,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elija una opción de la lista." type="list">
+    <dataValidation sqref="E2:E184" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elija una opción de la lista." type="list">
       <formula1>"Collao,Chanka,ambas,no sé"</formula1>
     </dataValidation>
   </dataValidations>
